--- a/Test_Cases/Test_scenarios_Doc.xlsx
+++ b/Test_Cases/Test_scenarios_Doc.xlsx
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dhruv\Desktop\QA_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9CE9AC9-50C4-416B-A056-5C6849177E4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10D8BC8F-EE31-4AC2-8B77-04CF5101960D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test_Scenarios" sheetId="2" r:id="rId1"/>
     <sheet name="Login_Test_Case" sheetId="3" r:id="rId2"/>
+    <sheet name="Register_Test_Case" sheetId="4" r:id="rId3"/>
+    <sheet name="Logout_Test Cases" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="251">
   <si>
     <t>Project Name</t>
   </si>
@@ -512,6 +514,304 @@
   <si>
     <t>Valid Email address : user@test.com
 Valid Password with leading space : Test@123</t>
+  </si>
+  <si>
+    <t>Test Case ID</t>
+  </si>
+  <si>
+    <t>Test Scenario</t>
+  </si>
+  <si>
+    <t>Test Data</t>
+  </si>
+  <si>
+    <t>TC_01</t>
+  </si>
+  <si>
+    <t>Verify register page opens</t>
+  </si>
+  <si>
+    <t>Click My Account &gt; Register</t>
+  </si>
+  <si>
+    <t>Register page should open</t>
+  </si>
+  <si>
+    <t>TC_02</t>
+  </si>
+  <si>
+    <t>Verify mandatory fields validation</t>
+  </si>
+  <si>
+    <t>Leave all fields empty and click continue</t>
+  </si>
+  <si>
+    <t>Error messages displayed</t>
+  </si>
+  <si>
+    <t>TC_03</t>
+  </si>
+  <si>
+    <t>Valid registration</t>
+  </si>
+  <si>
+    <t>Enter all valid details and submit</t>
+  </si>
+  <si>
+    <t>Valid data</t>
+  </si>
+  <si>
+    <t>Account created successfully</t>
+  </si>
+  <si>
+    <t>TC_04</t>
+  </si>
+  <si>
+    <t>Invalid email format</t>
+  </si>
+  <si>
+    <t>Enter invalid email and submit</t>
+  </si>
+  <si>
+    <t>abc@</t>
+  </si>
+  <si>
+    <t>Error for invalid email</t>
+  </si>
+  <si>
+    <t>TC_05</t>
+  </si>
+  <si>
+    <t>Password mismatch</t>
+  </si>
+  <si>
+    <t>Enter different password and confirm password</t>
+  </si>
+  <si>
+    <t>123 / 456</t>
+  </si>
+  <si>
+    <t>Error for mismatch</t>
+  </si>
+  <si>
+    <t>TC_06</t>
+  </si>
+  <si>
+    <t>Duplicate email</t>
+  </si>
+  <si>
+    <t>Register with existing email</t>
+  </si>
+  <si>
+    <t>existing@mail.com</t>
+  </si>
+  <si>
+    <t>Error: Email already exists</t>
+  </si>
+  <si>
+    <t>TC_07</t>
+  </si>
+  <si>
+    <t>Phone number validation</t>
+  </si>
+  <si>
+    <t>Enter invalid phone number</t>
+  </si>
+  <si>
+    <t>abc123</t>
+  </si>
+  <si>
+    <t>Error for phone</t>
+  </si>
+  <si>
+    <t>TC_08</t>
+  </si>
+  <si>
+    <t>Password strength</t>
+  </si>
+  <si>
+    <t>Enter weak password</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>Password strength warning</t>
+  </si>
+  <si>
+    <t>TC_09</t>
+  </si>
+  <si>
+    <t>Terms and conditions unchecked</t>
+  </si>
+  <si>
+    <t>Do not check T&amp;C and submit</t>
+  </si>
+  <si>
+    <t>Error for T&amp;C</t>
+  </si>
+  <si>
+    <t>Application is running on http://localhost/opencart
+User is on Register</t>
+  </si>
+  <si>
+    <t>Test Case Desription</t>
+  </si>
+  <si>
+    <t>TC_004</t>
+  </si>
+  <si>
+    <t>Logout button visibility</t>
+  </si>
+  <si>
+    <t>User logged in</t>
+  </si>
+  <si>
+    <t>Check UI</t>
+  </si>
+  <si>
+    <t>Logout button visible</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>TC_005</t>
+  </si>
+  <si>
+    <t>Direct logout URL access</t>
+  </si>
+  <si>
+    <t>User not logged in</t>
+  </si>
+  <si>
+    <t>Access logout URL</t>
+  </si>
+  <si>
+    <t>Redirect to login page</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>TC_006</t>
+  </si>
+  <si>
+    <t>Session timeout logout</t>
+  </si>
+  <si>
+    <t>Wait for session expiry</t>
+  </si>
+  <si>
+    <t>User auto logged out</t>
+  </si>
+  <si>
+    <t>TC_007</t>
+  </si>
+  <si>
+    <t>Logout after inactivity</t>
+  </si>
+  <si>
+    <t>Stay idle → logout</t>
+  </si>
+  <si>
+    <t>Session should end properly</t>
+  </si>
+  <si>
+    <t>TC_008</t>
+  </si>
+  <si>
+    <t>Browser refresh after logout</t>
+  </si>
+  <si>
+    <t>Logout → Refresh page</t>
+  </si>
+  <si>
+    <t>User should not be logged in</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>TC_009</t>
+  </si>
+  <si>
+    <t>Logout and re-login</t>
+  </si>
+  <si>
+    <t>Logout → Login again</t>
+  </si>
+  <si>
+    <t>User should login successfully</t>
+  </si>
+  <si>
+    <t>TC_010</t>
+  </si>
+  <si>
+    <t>Security defect - back button auto login</t>
+  </si>
+  <si>
+    <t>Logout → Success page → Press back button</t>
+  </si>
+  <si>
+    <t>User should NOT be auto logged in (BUG if accessed)</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>TC_011</t>
+  </si>
+  <si>
+    <t>Logout API/session clear validation</t>
+  </si>
+  <si>
+    <t>Logout → Check session</t>
+  </si>
+  <si>
+    <t>Session should be destroyed</t>
+  </si>
+  <si>
+    <t>Steps</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>TC_001</t>
+  </si>
+  <si>
+    <t>Logout from dashboard</t>
+  </si>
+  <si>
+    <t>Click logout button</t>
+  </si>
+  <si>
+    <t>User redirected to login page</t>
+  </si>
+  <si>
+    <t>TC_002</t>
+  </si>
+  <si>
+    <t>Logout session invalidation</t>
+  </si>
+  <si>
+    <t>Logout → Press back button</t>
+  </si>
+  <si>
+    <t>User should NOT access account page</t>
+  </si>
+  <si>
+    <t>TC_003</t>
+  </si>
+  <si>
+    <t>Logout with multiple tabs</t>
+  </si>
+  <si>
+    <t>Open 2 tabs → logout in one</t>
+  </si>
+  <si>
+    <t>All tabs should be logged out</t>
   </si>
 </sst>
 </file>
@@ -522,7 +822,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="dd\-mm\-yyyy"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -539,7 +839,7 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -548,18 +848,10 @@
     <font>
       <b/>
       <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <color theme="0"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="3">
@@ -576,7 +868,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -614,34 +906,65 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -654,17 +977,78 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -949,23 +1333,23 @@
   <dimension ref="A1:E38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="92.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.109375" customWidth="1"/>
+    <col min="3" max="3" width="25.33203125" customWidth="1"/>
+    <col min="4" max="4" width="53.33203125" customWidth="1"/>
+    <col min="5" max="5" width="18.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="14" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="20" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -973,571 +1357,571 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="21" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="22" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="23">
         <v>46118</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="18" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="8" t="s">
+    <row r="8" spans="1:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" s="9" t="s">
+      <c r="B8" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="17">
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="8" t="s">
+    <row r="9" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C9" s="9" t="s">
+      <c r="B9" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="17">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="8" t="s">
+    <row r="10" spans="1:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" s="9" t="s">
+      <c r="B10" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="17">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="8" t="s">
+    <row r="11" spans="1:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" s="9" t="s">
+      <c r="B11" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="17">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="8" t="s">
+    <row r="12" spans="1:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" s="9" t="s">
+      <c r="B12" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="17">
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="8" t="s">
+    <row r="13" spans="1:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" s="9" t="s">
+      <c r="B13" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="17">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="8" t="s">
+    <row r="14" spans="1:5" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" s="9" t="s">
+      <c r="B14" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="17">
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="8" t="s">
+    <row r="15" spans="1:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" s="9" t="s">
+      <c r="B15" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="8" t="s">
+    <row r="16" spans="1:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" s="9" t="s">
+      <c r="B16" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="17">
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="8" t="s">
+    <row r="17" spans="1:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" s="9" t="s">
+      <c r="B17" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="17">
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="8" t="s">
+    <row r="18" spans="1:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C18" s="9" t="s">
+      <c r="B18" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="17">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="8" t="s">
+    <row r="19" spans="1:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C19" s="9" t="s">
+      <c r="B19" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="17">
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="8" t="s">
+    <row r="20" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C20" s="9" t="s">
+      <c r="B20" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="8" t="s">
+    <row r="21" spans="1:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C21" s="9" t="s">
+      <c r="B21" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="17">
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="8" t="s">
+    <row r="22" spans="1:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C22" s="9" t="s">
+      <c r="B22" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="17">
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="8" t="s">
+    <row r="23" spans="1:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C23" s="9" t="s">
+      <c r="B23" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="17">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="8" t="s">
+    <row r="24" spans="1:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C24" s="9" t="s">
+      <c r="B24" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D24" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="E24" s="9">
+      <c r="E24" s="17">
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="8" t="s">
+    <row r="25" spans="1:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" s="9" t="s">
+      <c r="B25" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="D25" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="E25" s="9">
+      <c r="E25" s="17">
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="8" t="s">
+    <row r="26" spans="1:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C26" s="9" t="s">
+      <c r="B26" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="D26" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E26" s="17">
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="8" t="s">
+    <row r="27" spans="1:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B27" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C27" s="9" t="s">
+      <c r="B27" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="D27" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E27" s="9">
+      <c r="E27" s="17">
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="8" t="s">
+    <row r="28" spans="1:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="B28" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C28" s="9" t="s">
+      <c r="B28" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="E28" s="9">
+      <c r="E28" s="17">
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="8" t="s">
+    <row r="29" spans="1:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B29" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C29" s="9" t="s">
+      <c r="B29" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="17">
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="8" t="s">
+    <row r="30" spans="1:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B30" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C30" s="9" t="s">
+      <c r="B30" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="D30" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="E30" s="9">
+      <c r="E30" s="17">
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="8" t="s">
+    <row r="31" spans="1:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C31" s="9" t="s">
+      <c r="B31" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C31" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="D31" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="E31" s="9">
+      <c r="E31" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="8" t="s">
+    <row r="32" spans="1:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B32" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C32" s="10" t="s">
+      <c r="B32" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="D32" s="9" t="s">
+      <c r="D32" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="E32" s="9">
+      <c r="E32" s="17">
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="8" t="s">
+    <row r="33" spans="1:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="B33" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C33" s="10" t="s">
+      <c r="B33" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C33" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="D33" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="E33" s="9">
+      <c r="E33" s="17">
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="8" t="s">
+    <row r="34" spans="1:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B34" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C34" s="10" t="s">
+      <c r="B34" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C34" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="D34" s="9" t="s">
+      <c r="D34" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="E34" s="9">
+      <c r="E34" s="17">
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="8" t="s">
+    <row r="35" spans="1:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B35" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C35" s="10" t="s">
+      <c r="B35" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C35" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="D35" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="E35" s="9">
+      <c r="E35" s="17">
         <v>11</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="8" t="s">
+    <row r="36" spans="1:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="B36" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C36" s="10" t="s">
+      <c r="B36" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C36" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="D36" s="9" t="s">
+      <c r="D36" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="E36" s="9">
+      <c r="E36" s="17">
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="8" t="s">
+    <row r="37" spans="1:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B37" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C37" s="10" t="s">
+      <c r="B37" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C37" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="D37" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="E37" s="9">
+      <c r="E37" s="17">
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="8" t="s">
+    <row r="38" spans="1:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B38" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C38" s="10" t="s">
+      <c r="B38" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C38" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="D38" s="9" t="s">
+      <c r="D38" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="E38" s="9">
+      <c r="E38" s="17">
         <v>3</v>
       </c>
     </row>
@@ -1548,434 +1932,914 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFA2483B-B911-4B2B-87DF-CF9694B37B96}">
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="9.5546875" customWidth="1"/>
     <col min="3" max="3" width="27.21875" customWidth="1"/>
     <col min="4" max="4" width="28.5546875" customWidth="1"/>
-    <col min="5" max="5" width="23.33203125" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
-    <col min="7" max="7" width="16.88671875" customWidth="1"/>
-    <col min="8" max="8" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="28.6640625" customWidth="1"/>
+    <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-    </row>
-    <row r="2" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
+    </row>
+    <row r="2" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="I2" s="18"/>
-    </row>
-    <row r="3" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
+      <c r="I2" s="7"/>
+    </row>
+    <row r="3" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="I3" s="18"/>
-    </row>
-    <row r="4" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="I3" s="7"/>
+    </row>
+    <row r="4" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="H4" s="18" t="s">
+      <c r="H4" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="I4" s="18"/>
-    </row>
-    <row r="5" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
+      <c r="I4" s="7"/>
+    </row>
+    <row r="5" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="H5" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="I5" s="18"/>
-    </row>
-    <row r="6" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
+      <c r="I5" s="7"/>
+    </row>
+    <row r="6" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="H6" s="18" t="s">
+      <c r="H6" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="I6" s="18"/>
-    </row>
-    <row r="7" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="18" t="s">
+      <c r="I6" s="7"/>
+    </row>
+    <row r="7" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="H7" s="16" t="s">
+      <c r="H7" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="I7" s="2" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="18" t="s">
+    <row r="8" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="H8" s="16" t="s">
+      <c r="H8" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="I8" s="13" t="s">
+      <c r="I8" s="11" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="12"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="12"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="12"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="12"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F11E23BC-9EE6-429A-A72D-2C4CDD64644A}">
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.6640625" style="25" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="5" max="5" width="23.88671875" customWidth="1"/>
+    <col min="6" max="6" width="12.77734375" customWidth="1"/>
+    <col min="7" max="7" width="15.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="E1" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="G1" s="29" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="H2" s="24"/>
+    </row>
+    <row r="3" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H3" s="24"/>
+    </row>
+    <row r="4" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H4" s="24"/>
+    </row>
+    <row r="5" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H5" s="24"/>
+    </row>
+    <row r="6" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H6" s="24"/>
+    </row>
+    <row r="7" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H7" s="24"/>
+    </row>
+    <row r="8" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="H8" s="24"/>
+    </row>
+    <row r="9" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="H9" s="24"/>
+    </row>
+    <row r="10" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H10" s="24"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1DBBAF0-6AA3-45D5-A9D7-7C455A321A43}">
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="13.88671875" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" customWidth="1"/>
+    <col min="5" max="5" width="18.5546875" customWidth="1"/>
+    <col min="6" max="6" width="20.6640625" customWidth="1"/>
+    <col min="9" max="9" width="12.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="30" t="s">
+        <v>153</v>
+      </c>
+      <c r="D1" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="E1" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="F1" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="H1" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="I1" s="30" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>240</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>241</v>
+      </c>
+      <c r="F2" s="27" t="s">
+        <v>242</v>
+      </c>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3" t="s">
+        <v>223</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
